--- a/요구사항_정의서/요구사항_정의서_v8.xlsx
+++ b/요구사항_정의서/요구사항_정의서_v8.xlsx
@@ -468,7 +468,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>v7 대비 변경: REQ-001~049(+백로그 1건)를 클라이언트 그룹(공통/복약관리대상자/보호자/지원인력)별 시트로 재구성하고, User Story 형식과 REQ별 구현여부(완료/부분/미구현/확인필요)를 추가했습니다.</t>
+          <t>v7 대비 변경: REQ-001~049(+백로그 1건)를 클라이언트 그룹(공통/복약관리대상자/보호자/지원인력)별 시트로 재구성하고, User Story 형식과 REQ별 구현여부(완료/부분/미구현/확인필요)를 추가했습니다. 이후 2차 검토(서브에이전트 2라운드 교차검증, 2026-07-13)에서 백로그의 '개인/단체 회원가입 구분(보류)'이 이미 구현된 기능임을 확인해 REQ-050으로 승격하고 백로그에서 제거했습니다.</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>PII 필드 암호화는 구현(Fernet/HMAC). 전송 구간 암호화는 배포 환경(HTTPS) 의존이라 미배포 상태에서는 검증 불가</t>
+          <t>PII 필드 암호화는 구현(Fernet/HMAC). 전송 구간 암호화는 배포 환경(HTTPS) 의존이라 미배포 상태에서는 검증 불가. '최소권한 접근'은 monitoring_router.py/care_router.py에만 적용되고(get_current_actor/get_current_caregiver 다수), records_router.py/ocr_router.py/rag_router.py/chat_router.py는 인증 Depends가 0건이라 이 부분은 미적용(REQ-031과 동일 근거)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>생년월일(birth_date)만 구현. 주소(address)는 Patient/Caregiver 어디에도 없음, 특이사항은 Patient.note로만 부분 대응(Caregiver엔 없음). 주민등록번호는 정책상 미수집</t>
+          <t>생년월일(birth_date)만 구현. 주소(address)는 Patient/Caregiver 어디에도 없음, 특이사항은 Patient.note로만 부분 대응(Caregiver엔 없음). 주민등록번호는 정책상 미수집. 상세내용이 언급하는 'GET /users/me'는 실제 코드에 없는 경로이며(grep 결과 0건), 실질적으로는 GET /monitoring/patients·GET /monitoring/caregivers(둘 다 본인 범위로 필터링)가 그 역할을 한다</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4275,6 +4275,55 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>REQ-050</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>사용자관리</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>지원인력(요양보호사·생활지원사·사회복지사 소속 기관·단체)으로서, 개인이 아니라 기관 단위로 가입하고 기관명·기관유형·사업자등록번호·담당자 정보를 등록하고 싶다. 그래야 개인 계정과 별도로 기관 소속임을 시스템에 알리고 담당자가 로그인 계정을 관리할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>회원가입 시 개인(환자 본인/보호자) 가입과 별도로 기관(단체) 가입을 지원해야 한다. relation_type=organization으로 구분하고, 기관명(org_name)·기관유형(org_type)·사업자등록번호(business_reg_no)·담당자 이름(manager_name)·담당자 전화번호(manager_phone)를 입력받는다. 담당자 이메일은 별도 컬럼 없이 로그인 계정의 email 필드를 재사용한다.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>• relation_type=organization으로 기관 가입 구분
+• org_name/org_type/business_reg_no/manager_name/manager_phone 입력·저장
+• 담당자 이메일은 email(로그인 아이디)로 통합, 별도 컬럼 없음</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>backend/models.py:94,101~108 relation_type=organization + org_* 필드, monitoring_router.py:160~208 CaregiverCreate/CaregiverPublic/create_caregiver, frontend/src/pages/SignUp.tsx:12,249,356 기관 가입 UI — 전부 구현 확인</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>v6→v7 revision log에서 '개인/단체 회원가입 구분은 설계 미확정'이라며 백로그로 남겼던 항목 — 이후 실제로 구현 완료됨을 2026-07-13 코드·Figma 재검토로 확인해 정식 REQ로 승격, 백로그에서 제거(요구사항_정의서_v7_to_v8_revision_log.md 후속 수정 참고)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4286,7 +4335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4326,38 +4375,6 @@
       <c r="F1" s="6" t="inlineStr">
         <is>
           <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>(백로그)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>백로그</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>사용자관리</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>개인/단체 회원가입 구분(보류)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>회원가입 시 개인/단체 계정을 구분하자는 요청이 있으나, '단체'의 정의·로그인 단위·추가 서류(사업자등록번호 등) 등 설계 결정이 미확정이라 이번 버전 범위에서 제외한다. 정식 REQ 번호를 부여하지 않고 백로그로만 남긴다. 배경: docs/draft_signup_mentoring_feedback_v1.md.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>설계 확정(account_type/organizations 등) 후 정식 요구사항으로 승격 예정</t>
         </is>
       </c>
     </row>
